--- a/phase2/preparation/20261022/FDS_Phase2_Review_Operating_WBS_20261022.xlsx
+++ b/phase2/preparation/20261022/FDS_Phase2_Review_Operating_WBS_20261022.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Calendar" sheetId="1" r:id="R973cf23ae82444ca"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="WBS" sheetId="2" r:id="R0573f1fca4934577"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Calendar" sheetId="1" r:id="R861ea511669440d5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="WBS" sheetId="2" r:id="Rf23f3bc7c3a746fa"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -19,7 +19,7 @@
     <x:numFmt numFmtId="201" formatCode="0"/>
     <x:numFmt numFmtId="202" formatCode="yyyy-mm-dd"/>
   </x:numFmts>
-  <x:fonts count="5">
+  <x:fonts count="6">
     <x:font>
       <x:sz val="11"/>
       <x:name val="Carlito"/>
@@ -43,6 +43,10 @@
       <x:b/>
       <x:sz val="11"/>
       <x:name val="Malgun Gothic"/>
+    </x:font>
+    <x:font>
+      <x:sz val="11"/>
+      <x:name val="Arial"/>
     </x:font>
   </x:fonts>
   <x:fills count="4">
@@ -75,7 +79,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="18">
+  <x:cellXfs count="21">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -125,6 +129,15 @@
     </x:xf>
     <x:xf numFmtId="200" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="202" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
@@ -1174,7 +1187,9 @@
       <x:c r="J19" s="2"/>
     </x:row>
     <x:row r="20">
-      <x:c r="A20" s="2"/>
+      <x:c r="A20" s="2" t="str">
+        <x:v>10/25 Start·D22 운영 관리 반영</x:v>
+      </x:c>
       <x:c r="B20" s="2"/>
       <x:c r="C20" s="2"/>
       <x:c r="D20" s="2"/>
@@ -1186,62 +1201,142 @@
       <x:c r="J20" s="2"/>
     </x:row>
     <x:row r="21">
-      <x:c r="A21" s="2"/>
-      <x:c r="B21" s="2"/>
-      <x:c r="C21" s="2"/>
-      <x:c r="D21" s="2"/>
-      <x:c r="E21" s="2"/>
-      <x:c r="F21" s="2"/>
-      <x:c r="G21" s="2"/>
-      <x:c r="H21" s="2"/>
+      <x:c r="A21" s="9" t="str">
+        <x:v>Record ID</x:v>
+      </x:c>
+      <x:c r="B21" s="9" t="str">
+        <x:v>티켓</x:v>
+      </x:c>
+      <x:c r="C21" s="9" t="str">
+        <x:v>현재 판정</x:v>
+      </x:c>
+      <x:c r="D21" s="9" t="str">
+        <x:v>책임</x:v>
+      </x:c>
+      <x:c r="E21" s="9" t="str">
+        <x:v>기록일 (KST)</x:v>
+      </x:c>
+      <x:c r="F21" s="9" t="str">
+        <x:v>판정 범위</x:v>
+      </x:c>
+      <x:c r="G21" s="9" t="str">
+        <x:v>후속 담당</x:v>
+      </x:c>
+      <x:c r="H21" s="9" t="str">
+        <x:v>인계·잔여</x:v>
+      </x:c>
       <x:c r="I21" s="2"/>
       <x:c r="J21" s="2"/>
     </x:row>
-    <x:row r="22">
-      <x:c r="A22" s="2"/>
-      <x:c r="B22" s="2"/>
-      <x:c r="C22" s="2"/>
-      <x:c r="D22" s="2"/>
-      <x:c r="E22" s="2"/>
-      <x:c r="F22" s="2"/>
-      <x:c r="G22" s="2"/>
-      <x:c r="H22" s="2"/>
+    <x:row r="22" ht="66" customHeight="1">
+      <x:c r="A22" s="19" t="str">
+        <x:v>MS-P2-START-01</x:v>
+      </x:c>
+      <x:c r="B22" s="19" t="n">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="C22" s="19" t="str">
+        <x:v>Entry 확인·관리 기록</x:v>
+      </x:c>
+      <x:c r="D22" s="19" t="str">
+        <x:v>이권욱</x:v>
+      </x:c>
+      <x:c r="E22" s="20" t="d">
+        <x:v>2026-10-25T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="F22" s="19" t="str">
+        <x:v>선행조건/Decision/Risk 인계</x:v>
+      </x:c>
+      <x:c r="G22" s="19" t="str">
+        <x:v>권욱 및 각 Lead</x:v>
+      </x:c>
+      <x:c r="H22" s="19" t="str">
+        <x:v>G4·실제 배포·최종 Close는 개별 인수</x:v>
+      </x:c>
       <x:c r="I22" s="2"/>
       <x:c r="J22" s="2"/>
     </x:row>
-    <x:row r="23">
-      <x:c r="A23" s="2"/>
-      <x:c r="B23" s="2"/>
-      <x:c r="C23" s="2"/>
-      <x:c r="D23" s="2"/>
-      <x:c r="E23" s="2"/>
-      <x:c r="F23" s="2"/>
-      <x:c r="G23" s="2"/>
-      <x:c r="H23" s="2"/>
+    <x:row r="23" ht="66" customHeight="1">
+      <x:c r="A23" s="19" t="str">
+        <x:v>DEC-P2-REG-01</x:v>
+      </x:c>
+      <x:c r="B23" s="19" t="n">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="C23" s="19" t="str">
+        <x:v>FINAL_GO_HARBOR</x:v>
+      </x:c>
+      <x:c r="D23" s="19" t="str">
+        <x:v>이권욱</x:v>
+      </x:c>
+      <x:c r="E23" s="20" t="d">
+        <x:v>2026-10-25T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="F23" s="19" t="str">
+        <x:v>D22 선택·시험 정의·IF-19</x:v>
+      </x:c>
+      <x:c r="G23" s="19" t="str">
+        <x:v>하영·재환·권욱</x:v>
+      </x:c>
+      <x:c r="H23" s="19" t="str">
+        <x:v>ECR 수동 A 조건부/미활성. 실패 시 신규 rollout STOP</x:v>
+      </x:c>
       <x:c r="I23" s="2"/>
       <x:c r="J23" s="2"/>
     </x:row>
-    <x:row r="24">
-      <x:c r="A24" s="2"/>
-      <x:c r="B24" s="2"/>
-      <x:c r="C24" s="2"/>
-      <x:c r="D24" s="2"/>
-      <x:c r="E24" s="2"/>
-      <x:c r="F24" s="2"/>
-      <x:c r="G24" s="2"/>
-      <x:c r="H24" s="2"/>
+    <x:row r="24" ht="66" customHeight="1">
+      <x:c r="A24" s="19" t="str">
+        <x:v>P2-APP-01</x:v>
+      </x:c>
+      <x:c r="B24" s="19" t="n">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="C24" s="19" t="str">
+        <x:v>Harbor 소비 계약 연결</x:v>
+      </x:c>
+      <x:c r="D24" s="19" t="str">
+        <x:v>이재환</x:v>
+      </x:c>
+      <x:c r="E24" s="20" t="d">
+        <x:v>2026-10-25T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="F24" s="19" t="str">
+        <x:v>동일 2앱·6객체·digest</x:v>
+      </x:c>
+      <x:c r="G24" s="19" t="str">
+        <x:v>재환·하영</x:v>
+      </x:c>
+      <x:c r="H24" s="19" t="str">
+        <x:v>MSA42 merge. 앱 전체 AC·Runtime 판정은 별도</x:v>
+      </x:c>
       <x:c r="I24" s="2"/>
       <x:c r="J24" s="2"/>
     </x:row>
-    <x:row r="25">
-      <x:c r="A25" s="2"/>
-      <x:c r="B25" s="2"/>
-      <x:c r="C25" s="2"/>
-      <x:c r="D25" s="2"/>
-      <x:c r="E25" s="2"/>
-      <x:c r="F25" s="2"/>
-      <x:c r="G25" s="2"/>
-      <x:c r="H25" s="2"/>
+    <x:row r="25" ht="66" customHeight="1">
+      <x:c r="A25" s="19" t="str">
+        <x:v>P2-HYB-01</x:v>
+      </x:c>
+      <x:c r="B25" s="19" t="n">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="C25" s="19" t="str">
+        <x:v>IF-19 운영 결정 연결</x:v>
+      </x:c>
+      <x:c r="D25" s="19" t="str">
+        <x:v>이재환</x:v>
+      </x:c>
+      <x:c r="E25" s="20" t="d">
+        <x:v>2026-10-25T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="F25" s="19" t="str">
+        <x:v>node pull·TLS·P2 자격</x:v>
+      </x:c>
+      <x:c r="G25" s="19" t="str">
+        <x:v>하영·재환·권욱</x:v>
+      </x:c>
+      <x:c r="H25" s="19" t="str">
+        <x:v>Robot/Secret·SA 및 경로 최종 회수는 #12/#55</x:v>
+      </x:c>
       <x:c r="I25" s="2"/>
       <x:c r="J25" s="2"/>
     </x:row>
@@ -1258,7 +1353,9 @@
       <x:c r="J26" s="2"/>
     </x:row>
     <x:row r="27">
-      <x:c r="A27" s="2"/>
+      <x:c r="A27" s="2" t="str">
+        <x:v>현행 근거: ../20261023/acceptance-delta.md §10/25 관리 마감·IF-19</x:v>
+      </x:c>
       <x:c r="B27" s="2"/>
       <x:c r="C27" s="2"/>
       <x:c r="D27" s="2"/>
@@ -1270,7 +1367,9 @@
       <x:c r="J27" s="2"/>
     </x:row>
     <x:row r="28">
-      <x:c r="A28" s="2"/>
+      <x:c r="A28" s="2" t="str">
+        <x:v>기록일은 관리 반영일입니다. 과거 실제 착수·완료일은 합성하지 않았습니다.</x:v>
+      </x:c>
       <x:c r="B28" s="2"/>
       <x:c r="C28" s="2"/>
       <x:c r="D28" s="2"/>
@@ -1282,7 +1381,9 @@
       <x:c r="J28" s="2"/>
     </x:row>
     <x:row r="29">
-      <x:c r="A29" s="2"/>
+      <x:c r="A29" s="2" t="str">
+        <x:v>관리 시스템: GitHub 단일. 사용자 10/25 결정으로 Notion 미사용·연결 금지.</x:v>
+      </x:c>
       <x:c r="B29" s="2"/>
       <x:c r="C29" s="2"/>
       <x:c r="D29" s="2"/>
@@ -1294,7 +1395,9 @@
       <x:c r="J29" s="2"/>
     </x:row>
     <x:row r="30">
-      <x:c r="A30" s="2"/>
+      <x:c r="A30" s="2" t="str">
+        <x:v>발행 v3.1.22·Calendar 회의 계획 및 기존 WBS 일정·수식은 보존합니다.</x:v>
+      </x:c>
       <x:c r="B30" s="2"/>
       <x:c r="C30" s="2"/>
       <x:c r="D30" s="2"/>

--- a/phase2/preparation/20261022/FDS_Phase2_Review_Operating_WBS_20261022.xlsx
+++ b/phase2/preparation/20261022/FDS_Phase2_Review_Operating_WBS_20261022.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Calendar" sheetId="1" r:id="R861ea511669440d5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="WBS" sheetId="2" r:id="Rf23f3bc7c3a746fa"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Calendar" sheetId="1" r:id="Rc425c03493ad4a14"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="WBS" sheetId="2" r:id="Reb9bf54975d045b0"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -1408,6 +1408,210 @@
       <x:c r="I30" s="2"/>
       <x:c r="J30" s="2"/>
     </x:row>
+    <x:row r="32">
+      <x:c r="A32" s="2" t="str">
+        <x:v>10/25 관리 5건 종결·잔여 인계</x:v>
+      </x:c>
+      <x:c r="B32" s="2"/>
+      <x:c r="C32" s="2"/>
+      <x:c r="D32" s="2"/>
+      <x:c r="E32" s="2"/>
+      <x:c r="F32" s="2"/>
+      <x:c r="G32" s="2"/>
+      <x:c r="H32" s="2"/>
+    </x:row>
+    <x:row r="33">
+      <x:c r="A33" s="9" t="str">
+        <x:v>Record ID</x:v>
+      </x:c>
+      <x:c r="B33" s="9" t="str">
+        <x:v>티켓</x:v>
+      </x:c>
+      <x:c r="C33" s="9" t="str">
+        <x:v>관리 상태</x:v>
+      </x:c>
+      <x:c r="D33" s="9" t="str">
+        <x:v>기술 판정</x:v>
+      </x:c>
+      <x:c r="E33" s="9" t="str">
+        <x:v>담당</x:v>
+      </x:c>
+      <x:c r="F33" s="9" t="str">
+        <x:v>기록일 (KST)</x:v>
+      </x:c>
+      <x:c r="G33" s="9" t="str">
+        <x:v>후속 티켓</x:v>
+      </x:c>
+      <x:c r="H33" s="9" t="str">
+        <x:v>인계·잔여</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="34" ht="94" customHeight="1">
+      <x:c r="A34" s="19" t="str">
+        <x:v>MS-G4-01</x:v>
+      </x:c>
+      <x:c r="B34" s="19" t="n">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="C34" s="19" t="str">
+        <x:v>Done</x:v>
+      </x:c>
+      <x:c r="D34" s="19" t="str">
+        <x:v>미충족 유지</x:v>
+      </x:c>
+      <x:c r="E34" s="20" t="str">
+        <x:v>이권욱</x:v>
+      </x:c>
+      <x:c r="F34" s="20" t="d">
+        <x:v>2026-10-25T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="G34" s="19" t="str">
+        <x:v>#37 / #55 / #57</x:v>
+      </x:c>
+      <x:c r="H34" s="19" t="str">
+        <x:v>T6 INCONCLUSIVE. G4 PASS 아님. 실제 증적·잔여 후속 인계.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="35" ht="94" customHeight="1">
+      <x:c r="A35" s="19" t="str">
+        <x:v>MS-G6-01</x:v>
+      </x:c>
+      <x:c r="B35" s="19" t="n">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="C35" s="19" t="str">
+        <x:v>Done</x:v>
+      </x:c>
+      <x:c r="D35" s="19" t="str">
+        <x:v>미충족 유지</x:v>
+      </x:c>
+      <x:c r="E35" s="20" t="str">
+        <x:v>이권욱</x:v>
+      </x:c>
+      <x:c r="F35" s="20" t="d">
+        <x:v>2026-10-25T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="G35" s="19" t="str">
+        <x:v>#47 / #50 / #55</x:v>
+      </x:c>
+      <x:c r="H35" s="19" t="str">
+        <x:v>Hybrid·정책·E2E 미충족. G6 PASS 아님. 원 실행 티켓 유지.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="36" ht="94" customHeight="1">
+      <x:c r="A36" s="19" t="str">
+        <x:v>P2-DOC-01</x:v>
+      </x:c>
+      <x:c r="B36" s="19" t="n">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="C36" s="19" t="str">
+        <x:v>Done</x:v>
+      </x:c>
+      <x:c r="D36" s="19" t="str">
+        <x:v>후속 포함 고정</x:v>
+      </x:c>
+      <x:c r="E36" s="20" t="str">
+        <x:v>이권욱</x:v>
+      </x:c>
+      <x:c r="F36" s="20" t="d">
+        <x:v>2026-10-25T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="G36" s="19" t="str">
+        <x:v>#46 / #55 / #57</x:v>
+      </x:c>
+      <x:c r="H36" s="19" t="str">
+        <x:v>19개 저장소·증적·Known Issue 목록 고정. 이후 결과는 추가 기록.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="37" ht="94" customHeight="1">
+      <x:c r="A37" s="19" t="str">
+        <x:v>MS-DELIVERABLE-FREEZE-01</x:v>
+      </x:c>
+      <x:c r="B37" s="19" t="n">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="C37" s="19" t="str">
+        <x:v>Done</x:v>
+      </x:c>
+      <x:c r="D37" s="19" t="str">
+        <x:v>관리 후보 고정</x:v>
+      </x:c>
+      <x:c r="E37" s="20" t="str">
+        <x:v>이권욱</x:v>
+      </x:c>
+      <x:c r="F37" s="20" t="d">
+        <x:v>2026-10-25T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="G37" s="19" t="str">
+        <x:v>#46 / #55 / #57</x:v>
+      </x:c>
+      <x:c r="H37" s="19" t="str">
+        <x:v>오늘 관리 후보 세트만 고정. 새 결과로 원문을 소급 교체하지 않음.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="38" ht="94" customHeight="1">
+      <x:c r="A38" s="19" t="str">
+        <x:v>MS-P2-REVIEW-01</x:v>
+      </x:c>
+      <x:c r="B38" s="19" t="n">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="C38" s="19" t="str">
+        <x:v>Done</x:v>
+      </x:c>
+      <x:c r="D38" s="19" t="str">
+        <x:v>개최·인계 수용</x:v>
+      </x:c>
+      <x:c r="E38" s="20" t="str">
+        <x:v>이권욱</x:v>
+      </x:c>
+      <x:c r="F38" s="20" t="d">
+        <x:v>2026-10-25T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="G38" s="19" t="str">
+        <x:v>#46 / #55 / #57</x:v>
+      </x:c>
+      <x:c r="H38" s="19" t="str">
+        <x:v>10/23 개최 사용자 확인·회고 수용. 잔여 Action은 후속 티켓에 인계.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="40">
+      <x:c r="A40" s="2" t="str">
+        <x:v>관리 Done은 기술 AC PASS가 아닙니다. 미실행·미충족 원본을 그대로 보존합니다.</x:v>
+      </x:c>
+      <x:c r="B40" s="2"/>
+      <x:c r="C40" s="2"/>
+      <x:c r="D40" s="2"/>
+      <x:c r="E40" s="2"/>
+      <x:c r="F40" s="2"/>
+      <x:c r="G40" s="2"/>
+      <x:c r="H40" s="2"/>
+    </x:row>
+    <x:row r="41">
+      <x:c r="A41" s="2" t="str">
+        <x:v>근거: ../20261025/management-closeout.md 및 frozen-management-candidates.json</x:v>
+      </x:c>
+      <x:c r="B41" s="2"/>
+      <x:c r="C41" s="2"/>
+      <x:c r="D41" s="2"/>
+      <x:c r="E41" s="2"/>
+      <x:c r="F41" s="2"/>
+      <x:c r="G41" s="2"/>
+      <x:c r="H41" s="2"/>
+    </x:row>
+    <x:row r="42">
+      <x:c r="A42" s="2" t="str">
+        <x:v>운영계획·Calendar 수식·발행 정본 유지. 후속 결과는 #46/#55/#57에 기록합니다.</x:v>
+      </x:c>
+      <x:c r="B42" s="2"/>
+      <x:c r="C42" s="2"/>
+      <x:c r="D42" s="2"/>
+      <x:c r="E42" s="2"/>
+      <x:c r="F42" s="2"/>
+      <x:c r="G42" s="2"/>
+      <x:c r="H42" s="2"/>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
